--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487530_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487530_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.2832</v>
+        <v>7.2881</v>
       </c>
       <c r="E2" t="n">
-        <v>8.489699999999999</v>
+        <v>8.360900000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.2065</v>
+        <v>-1.0728</v>
       </c>
       <c r="G2" t="n">
         <v>3.4237</v>
@@ -610,13 +610,13 @@
         <v>2.546</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.5114</v>
+        <v>-0.5065</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.0612</v>
+        <v>-0.19</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4502</v>
+        <v>-0.3166</v>
       </c>
       <c r="V2" t="n">
         <v>1.8249</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.8111</v>
+        <v>3.1019</v>
       </c>
       <c r="E3" t="n">
-        <v>1.9868</v>
+        <v>2.2509</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8243</v>
+        <v>0.851</v>
       </c>
       <c r="G3" t="n">
         <v>2.5381</v>
@@ -688,13 +688,13 @@
         <v>1.1751</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.902</v>
+        <v>-0.6112</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5346</v>
+        <v>-0.2705</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3674</v>
+        <v>-0.3407</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6665</v>
+        <v>1.3283</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7769</v>
+        <v>2.305</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.1104</v>
+        <v>-0.9767</v>
       </c>
       <c r="G4" t="n">
         <v>-0.8308</v>
@@ -766,13 +766,13 @@
         <v>1.9585</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.2113</v>
+        <v>-0.5495</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6246</v>
+        <v>-0.0965</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.5867</v>
+        <v>-0.453</v>
       </c>
       <c r="V4" t="n">
         <v>2.7086</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. QITTANE</t>
+          <t>F. CORNALIS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,58 +799,58 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4942</v>
+        <v>-0.3837</v>
       </c>
       <c r="E5" t="n">
-        <v>1.5225</v>
+        <v>0.0204</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.0282</v>
+        <v>-0.4042</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.6625</v>
+        <v>-0.3837</v>
       </c>
       <c r="H5" t="n">
-        <v>1.4947</v>
+        <v>0.0204</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.1572</v>
+        <v>-0.4042</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8114</v>
+        <v>0.0204</v>
       </c>
       <c r="K5" t="n">
-        <v>1.4936</v>
+        <v>0.0204</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.6822</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.4739</v>
+        <v>-0.4042</v>
       </c>
       <c r="N5" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.475</v>
+        <v>-0.4042</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.7834</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9792</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.1958</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1.9401</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>1.6903</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2498</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>F. CORNALIS</t>
+          <t>M. QITTANE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,58 +877,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.3837</v>
+        <v>-0.5337</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0204</v>
+        <v>0.6014</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4042</v>
+        <v>-1.1352</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.3837</v>
+        <v>-0.6625</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0204</v>
+        <v>1.4947</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4042</v>
+        <v>-2.1572</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0204</v>
+        <v>0.8114</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0204</v>
+        <v>1.4936</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>-0.6822</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.4042</v>
+        <v>-1.4739</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.4042</v>
+        <v>-1.475</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>-0.7834</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.9792</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>0.1958</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>0.9122</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>0.7693</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>0.1429</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>G. GONZALEZ GARCIA</t>
+          <t>M. CAMBON DOMINGUEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.2879</v>
+        <v>-0.7991</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1679</v>
+        <v>1.5863</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.12</v>
+        <v>-2.3854</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.5038</v>
+        <v>-0.7431</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4931</v>
+        <v>0.8735000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.0107</v>
+        <v>-1.6166</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.7601</v>
+        <v>2.412</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3214</v>
+        <v>1.7557</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.0816</v>
+        <v>0.6563</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.7437</v>
+        <v>-3.1551</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.8145</v>
+        <v>-0.8822</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.9292</v>
+        <v>-2.2729</v>
       </c>
       <c r="P7" t="n">
-        <v>1.7626</v>
+        <v>0.9792</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.9792</v>
       </c>
       <c r="R7" t="n">
-        <v>1.7626</v>
+        <v>1.9585</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5467</v>
+        <v>-0.094</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5921999999999999</v>
+        <v>-0.1218</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.1389</v>
+        <v>0.0278</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-0.9412</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.2754</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Q. HUANG</t>
+          <t>G. GONZALEZ GARCIA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.7336</v>
+        <v>-1.5635</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2033</v>
+        <v>-0.5772</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.937</v>
+        <v>-0.9863</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.4177</v>
+        <v>-2.5038</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0269</v>
+        <v>-0.4931</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4446</v>
+        <v>-2.0107</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7219</v>
+        <v>-0.7601</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6362</v>
+        <v>0.3214</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0857</v>
+        <v>-1.0816</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.1395</v>
+        <v>-1.7437</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.6093</v>
+        <v>-0.8145</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.5302</v>
+        <v>-0.9292</v>
       </c>
       <c r="P8" t="n">
-        <v>0.5875</v>
+        <v>1.7626</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9792</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5668</v>
+        <v>1.7626</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6293</v>
+        <v>-0.8224</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.09</v>
+        <v>0.1829</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5393</v>
+        <v>-1.0053</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.2742</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.5507</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.8249</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. CAMBON DOMINGUEZ</t>
+          <t>D. MASEDA SOILAN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.7436</v>
+        <v>-1.7981</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4012</v>
+        <v>-0.927</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.1449</v>
+        <v>-0.8711</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.7431</v>
+        <v>-1.3497</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8735000000000001</v>
+        <v>-0.4202</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.6166</v>
+        <v>-0.9295</v>
       </c>
       <c r="J9" t="n">
-        <v>2.412</v>
+        <v>0.2534</v>
       </c>
       <c r="K9" t="n">
-        <v>1.7557</v>
+        <v>-0.5597</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6563</v>
+        <v>0.8131</v>
       </c>
       <c r="M9" t="n">
-        <v>-3.1551</v>
+        <v>-1.6031</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.8822</v>
+        <v>0.1396</v>
       </c>
       <c r="O9" t="n">
-        <v>-2.2729</v>
+        <v>-1.7427</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9792</v>
+        <v>0.1958</v>
       </c>
       <c r="Q9" t="n">
         <v>-0.9792</v>
       </c>
       <c r="R9" t="n">
-        <v>1.9585</v>
+        <v>1.1751</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.0385</v>
+        <v>-0.0935</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.3068</v>
+        <v>-0.2011</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2684</v>
+        <v>0.1076</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.9412</v>
+        <v>-0.5507</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2754</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2166</v>
+        <v>-0.5507</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. MASEDA SOILAN</t>
+          <t>Q. HUANG</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.4286</v>
+        <v>-1.8195</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.5575</v>
+        <v>0.1175</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.8711</v>
+        <v>-1.937</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.3497</v>
+        <v>-0.4177</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.4202</v>
+        <v>0.0269</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.9295</v>
+        <v>-0.4446</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2534</v>
+        <v>0.7219</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.5597</v>
+        <v>0.6362</v>
       </c>
       <c r="L10" t="n">
-        <v>0.8131</v>
+        <v>0.0857</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.6031</v>
+        <v>-1.1395</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1396</v>
+        <v>-0.6093</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.7427</v>
+        <v>-0.5302</v>
       </c>
       <c r="P10" t="n">
-        <v>0.1958</v>
+        <v>0.5875</v>
       </c>
       <c r="Q10" t="n">
         <v>-0.9792</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1751</v>
+        <v>1.5668</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.724</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8316</v>
+        <v>-0.1759</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1076</v>
+        <v>-0.5393</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.5507</v>
+        <v>-1.2742</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.5507</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.5507</v>
+        <v>-1.8249</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.3016</v>
+        <v>-4.8295</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.0525</v>
+        <v>-1.6071</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.2491</v>
+        <v>-3.2224</v>
       </c>
       <c r="G11" t="n">
         <v>-1.9521</v>
@@ -1312,13 +1312,13 @@
         <v>1.1751</v>
       </c>
       <c r="S11" t="n">
-        <v>0.6758999999999999</v>
+        <v>0.1481</v>
       </c>
       <c r="T11" t="n">
-        <v>0.7705</v>
+        <v>0.2158</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0945</v>
+        <v>-0.0678</v>
       </c>
       <c r="V11" t="n">
         <v>-4.2005</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.305</v>
+        <v>-5.0291</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.3226</v>
+        <v>-3.9397</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.9825</v>
+        <v>-1.0894</v>
       </c>
       <c r="G12" t="n">
         <v>-4.9197</v>
@@ -1390,13 +1390,13 @@
         <v>1.1751</v>
       </c>
       <c r="S12" t="n">
-        <v>0.06519999999999999</v>
+        <v>0.3411</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3276</v>
+        <v>0.0553</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3928</v>
+        <v>0.2858</v>
       </c>
       <c r="V12" t="n">
         <v>0.3329</v>
@@ -1423,19 +1423,19 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.928999999999998</v>
+        <v>-5.0379</v>
       </c>
       <c r="E13" t="n">
-        <v>7.300299999999999</v>
+        <v>8.1914</v>
       </c>
       <c r="F13" t="n">
-        <v>-13.2296</v>
+        <v>-13.2295</v>
       </c>
       <c r="G13" t="n">
         <v>-7.801299999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.3489</v>
+        <v>-0.3489000000000004</v>
       </c>
       <c r="I13" t="n">
         <v>-7.4526</v>
@@ -1468,13 +1468,13 @@
         <v>14.6886</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.882</v>
+        <v>-1.9909</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.7234000000000002</v>
+        <v>0.1674999999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>-2.1584</v>
+        <v>-2.1586</v>
       </c>
       <c r="V13" t="n">
         <v>-2.1002</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>9.2753</v>
+        <v>9.6136</v>
       </c>
       <c r="E14" t="n">
-        <v>9.3955</v>
+        <v>9.600199999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.1203</v>
+        <v>0.0134</v>
       </c>
       <c r="G14" t="n">
         <v>7.7915</v>
@@ -1546,13 +1546,13 @@
         <v>1.5668</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.2367</v>
+        <v>0.1016</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.0547</v>
+        <v>0.15</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.182</v>
+        <v>-0.0484</v>
       </c>
       <c r="V14" t="n">
         <v>0.1537</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>C. IGLESIAS GONZALEZ</t>
+          <t>E. OGUNFOLU</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.3052</v>
+        <v>2.168</v>
       </c>
       <c r="E15" t="n">
-        <v>4.2377</v>
+        <v>1.4469</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.9325</v>
+        <v>0.7211</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.1081</v>
+        <v>1.5599</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.6587</v>
+        <v>1.2818</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.4494</v>
+        <v>0.2781</v>
       </c>
       <c r="J15" t="n">
-        <v>0.8221000000000001</v>
+        <v>1.8683</v>
       </c>
       <c r="K15" t="n">
-        <v>0.08500000000000001</v>
+        <v>1.6161</v>
       </c>
       <c r="L15" t="n">
-        <v>0.7371</v>
+        <v>0.2521</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.9302</v>
+        <v>-0.3084</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.7437</v>
+        <v>-0.3344</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.1865</v>
+        <v>0.026</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>0.1958</v>
       </c>
       <c r="Q15" t="n">
         <v>-0.9792</v>
       </c>
       <c r="R15" t="n">
-        <v>0.9792</v>
+        <v>1.1751</v>
       </c>
       <c r="S15" t="n">
-        <v>2.9213</v>
+        <v>-0.0168</v>
       </c>
       <c r="T15" t="n">
-        <v>1.4109</v>
+        <v>-0.2682</v>
       </c>
       <c r="U15" t="n">
-        <v>1.5104</v>
+        <v>0.2514</v>
       </c>
       <c r="V15" t="n">
-        <v>1.492</v>
+        <v>0.4291</v>
       </c>
       <c r="W15" t="n">
-        <v>2.9839</v>
+        <v>0.8260999999999999</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.492</v>
+        <v>-0.397</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>E. OGUNFOLU</t>
+          <t>C. IGLESIAS GONZALEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.2398</v>
+        <v>1.6044</v>
       </c>
       <c r="E16" t="n">
-        <v>1.0376</v>
+        <v>3.419</v>
       </c>
       <c r="F16" t="n">
-        <v>1.2023</v>
+        <v>-1.8146</v>
       </c>
       <c r="G16" t="n">
-        <v>1.5599</v>
+        <v>-1.1081</v>
       </c>
       <c r="H16" t="n">
-        <v>1.2818</v>
+        <v>-0.6587</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2781</v>
+        <v>-0.4494</v>
       </c>
       <c r="J16" t="n">
-        <v>1.8683</v>
+        <v>0.8221000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>1.6161</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2521</v>
+        <v>0.7371</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.3084</v>
+        <v>-1.9302</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.3344</v>
+        <v>-0.7437</v>
       </c>
       <c r="O16" t="n">
-        <v>0.026</v>
+        <v>-1.1865</v>
       </c>
       <c r="P16" t="n">
-        <v>0.1958</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>-0.9792</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1751</v>
+        <v>0.9792</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0551</v>
+        <v>1.2205</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6775</v>
+        <v>0.5921999999999999</v>
       </c>
       <c r="U16" t="n">
-        <v>0.7326</v>
+        <v>0.6283</v>
       </c>
       <c r="V16" t="n">
-        <v>0.4291</v>
+        <v>1.492</v>
       </c>
       <c r="W16" t="n">
-        <v>0.8260999999999999</v>
+        <v>2.9839</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.397</v>
+        <v>-1.492</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0594</v>
+        <v>0.6115</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.0056</v>
+        <v>0.199</v>
       </c>
       <c r="F17" t="n">
-        <v>0.065</v>
+        <v>0.4125</v>
       </c>
       <c r="G17" t="n">
         <v>0.6582</v>
@@ -1780,13 +1780,13 @@
         <v>1.1751</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.3769</v>
+        <v>-0.8247</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5764</v>
+        <v>-0.3717</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.8005</v>
+        <v>-0.453</v>
       </c>
       <c r="V17" t="n">
         <v>-0.397</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. LUIS</t>
+          <t>J. NIETO GONZALEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2672</v>
+        <v>0.3499</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0408</v>
+        <v>1.4347</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.3081</v>
+        <v>-1.0848</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.0445</v>
+        <v>-0.0017</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.9133</v>
+        <v>0.867</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1313</v>
+        <v>-0.8687</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.6414</v>
+        <v>1.2024</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.6414</v>
+        <v>1.0003</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>0.2021</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.4031</v>
+        <v>-1.2041</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2719</v>
+        <v>-0.1333</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.1313</v>
+        <v>-1.0708</v>
       </c>
       <c r="P18" t="n">
-        <v>0.1958</v>
+        <v>0.7834</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.1958</v>
+        <v>0.7834</v>
       </c>
       <c r="S18" t="n">
-        <v>0.5814</v>
+        <v>0.2982</v>
       </c>
       <c r="T18" t="n">
-        <v>0.6822</v>
+        <v>0.2323</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1008</v>
+        <v>0.0659</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-0.73</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.73</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. NIETO GONZALEZ</t>
+          <t>J. LUIS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3756</v>
+        <v>-0.5208</v>
       </c>
       <c r="E19" t="n">
-        <v>0.923</v>
+        <v>-0.2662</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.2987</v>
+        <v>-0.2546</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.0017</v>
+        <v>-1.0445</v>
       </c>
       <c r="H19" t="n">
-        <v>0.867</v>
+        <v>-0.9133</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.8687</v>
+        <v>-0.1313</v>
       </c>
       <c r="J19" t="n">
-        <v>1.2024</v>
+        <v>-0.6414</v>
       </c>
       <c r="K19" t="n">
-        <v>1.0003</v>
+        <v>-0.6414</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2021</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.2041</v>
+        <v>-0.4031</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.1333</v>
+        <v>-0.2719</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.0708</v>
+        <v>-0.1313</v>
       </c>
       <c r="P19" t="n">
-        <v>0.7834</v>
+        <v>0.1958</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.7834</v>
+        <v>0.1958</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4273</v>
+        <v>0.3279</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2794</v>
+        <v>0.3752</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.148</v>
+        <v>-0.0473</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.73</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.73</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.552</v>
+        <v>-1.2672</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.9982</v>
+        <v>-0.7936</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.5538</v>
+        <v>-0.4736</v>
       </c>
       <c r="G20" t="n">
         <v>-0.5668</v>
@@ -2014,13 +2014,13 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0059</v>
+        <v>0.2789</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0594</v>
+        <v>0.1453</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0535</v>
+        <v>0.1337</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.6565</v>
+        <v>-2.1055</v>
       </c>
       <c r="E21" t="n">
-        <v>0.6516</v>
+        <v>-0.0648</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.3081</v>
+        <v>-2.0407</v>
       </c>
       <c r="G21" t="n">
         <v>-0.0633</v>
@@ -2092,13 +2092,13 @@
         <v>0.9792</v>
       </c>
       <c r="S21" t="n">
-        <v>1.8573</v>
+        <v>1.4083</v>
       </c>
       <c r="T21" t="n">
-        <v>1.785</v>
+        <v>1.0686</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0723</v>
+        <v>0.3397</v>
       </c>
       <c r="V21" t="n">
         <v>-1.492</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.0993</v>
+        <v>-4.5249</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.0529</v>
+        <v>-1.7459</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.0463</v>
+        <v>-2.779</v>
       </c>
       <c r="G22" t="n">
         <v>0.5766</v>
@@ -2170,13 +2170,13 @@
         <v>0.9792</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4864</v>
+        <v>0.08790000000000001</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0723</v>
+        <v>0.2347</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.414</v>
+        <v>-0.1467</v>
       </c>
       <c r="V22" t="n">
         <v>2.6445</v>
@@ -2203,19 +2203,19 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>5.929099999999999</v>
+        <v>5.929000000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>13.2295</v>
+        <v>13.2293</v>
       </c>
       <c r="F23" t="n">
-        <v>-7.3005</v>
+        <v>-7.3003</v>
       </c>
       <c r="G23" t="n">
         <v>7.801800000000001</v>
       </c>
       <c r="H23" t="n">
-        <v>0.349</v>
+        <v>0.3490000000000004</v>
       </c>
       <c r="I23" t="n">
         <v>7.452700000000001</v>
@@ -2248,13 +2248,13 @@
         <v>7.8338</v>
       </c>
       <c r="S23" t="n">
-        <v>2.8819</v>
+        <v>2.8818</v>
       </c>
       <c r="T23" t="n">
         <v>2.1584</v>
       </c>
       <c r="U23" t="n">
-        <v>0.7235</v>
+        <v>0.7236</v>
       </c>
       <c r="V23" t="n">
         <v>2.1003</v>
